--- a/results/event_aep_analysis_run_g8_mindur7.xlsx
+++ b/results/event_aep_analysis_run_g8_mindur7.xlsx
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-07-29 19:11:25</t>
+          <t>2025-07-30 13:15:48</t>
         </is>
       </c>
     </row>
